--- a/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/905/905_197311_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -739,13 +730,13 @@
         <v>389.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>88.3</v>
+        <v>28.3</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.5</v>
@@ -760,19 +751,19 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2</v>
@@ -790,7 +781,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>20.3</v>
@@ -819,7 +810,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.6</v>
+        <v>431.6</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>98.59999999999999</v>
@@ -830,11 +821,11 @@
       <c r="F5" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>121</v>
+      <c r="G5" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -858,7 +849,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
@@ -870,10 +861,10 @@
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>84.3</v>
+        <v>74.3</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
@@ -881,7 +872,7 @@
       <c r="W5" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y5" s="3" t="n">
@@ -904,7 +895,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>494.4</v>
+        <v>484.4</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
@@ -916,17 +907,17 @@
       <c r="G6" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>25.2</v>
+      <c r="H6" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>15.7</v>
+        <v>5.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.2</v>
@@ -935,7 +926,7 @@
         <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -961,7 +952,7 @@
       <c r="V6" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -971,7 +962,7 @@
         <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -987,7 +978,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>384.4</v>
+        <v>374.4</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
@@ -1003,7 +994,7 @@
         <v>12.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.8</v>
@@ -1021,7 +1012,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89.8</v>
+        <v>22.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1036,7 +1027,7 @@
         <v>24.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>18.7</v>
+        <v>68.7</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>11.4</v>
@@ -1073,7 +1064,7 @@
         <v>460.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>28.4</v>
+        <v>22.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>17</v>
@@ -1155,7 +1146,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2240.4</v>
+        <v>2140.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>142</v>
@@ -1167,10 +1158,10 @@
         <v>12.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>259.1</v>
+        <v>59.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>671.7</v>
+        <v>67.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
@@ -1189,13 +1180,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>343.3</v>
+        <v>345.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1272.1</v>
+        <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>110.9</v>
@@ -1210,13 +1201,13 @@
         <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>28.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>92.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>63.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>445.1</v>
@@ -1243,8 +1234,8 @@
       <c r="D10" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>66.09999999999999</v>
+      <c r="E10" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.5</v>
@@ -1252,19 +1243,19 @@
       <c r="G10" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>18.5</v>
+      <c r="H10" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1278,16 +1269,16 @@
         <v>0.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>26.4</v>
+        <v>25.4</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1041.4</v>
+        <v>1214.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
@@ -1305,7 +1296,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>161.4</v>
+        <v>1811.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1333,13 +1324,13 @@
         <v>21.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>92.8</v>
+      <c r="I11" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>5.1</v>
@@ -1352,7 +1343,7 @@
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
@@ -1379,8 +1370,8 @@
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>822</v>
+      <c r="X11" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1428,8 +1419,8 @@
       <c r="K12" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>81.40000000000001</v>
+      <c r="L12" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>17.6</v>
@@ -1446,10 +1437,10 @@
       <c r="Q12" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T12" s="3" t="n">
@@ -1498,27 +1489,27 @@
       <c r="F13" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="8" t="n">
-        <v>21</v>
+      <c r="J13" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
@@ -1536,7 +1527,7 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>27.5</v>
+        <v>77.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.8</v>
@@ -1578,8 +1569,8 @@
       <c r="E14" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>821.1</v>
+      <c r="F14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>7.4</v>
@@ -1589,7 +1580,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>1.2</v>
+        <v>121.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1601,13 +1592,13 @@
         <v>17.2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>12.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>21</v>
@@ -1615,7 +1606,7 @@
       <c r="R14" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1634,7 +1625,7 @@
         <v>22.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0.7</v>
@@ -1661,8 +1652,8 @@
       <c r="E15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>8.5</v>
+      <c r="F15" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.7</v>
@@ -1671,13 +1662,13 @@
         <v>14.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>17.2</v>
@@ -1695,18 +1686,18 @@
         <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>59.3</v>
       </c>
-      <c r="U15" s="8" t="n">
+      <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V15" s="3" t="n">
@@ -1719,10 +1710,10 @@
         <v>20.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1729,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1361.8</v>
+        <v>1561.8</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>134</v>
@@ -1750,19 +1741,19 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>481.4</v>
+        <v>48.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>73</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>88.8</v>
@@ -1771,25 +1762,25 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1465.9</v>
+        <v>465.9</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1089.3</v>
+        <v>119.3</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>2116.6</v>
+        <v>114.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>199.8</v>
+        <v>393.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>35.1</v>
@@ -1798,13 +1789,13 @@
         <v>101.9</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>969.1</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>98.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>458.4</v>
+        <v>457.4</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1821,16 +1812,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2312.4</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>40.1</v>
+        <v>312.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>29.7</v>
@@ -1839,19 +1830,19 @@
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.9</v>
@@ -1865,29 +1856,29 @@
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <v>189.1</v>
+      <c r="R17" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>29.9</v>
+        <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>789.1</v>
+        <v>788.1</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>211.6</v>
+      <c r="V17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2812.1</v>
+        <v>202.2</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1914,13 +1905,13 @@
       <c r="E18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>90.90000000000001</v>
+      <c r="F18" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
@@ -1930,7 +1921,7 @@
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>18.2</v>
@@ -1939,13 +1930,13 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>9.6</v>
@@ -1954,25 +1945,25 @@
         <v>21.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.5</v>
+        <v>66.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>14.7</v>
+        <v>11.7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22488.4</v>
+        <v>22621.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>111.1</v>
+        <v>1421.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>118.9</v>
+        <v>18.9</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>20.7</v>
@@ -1991,7 +1982,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>219.4</v>
+        <v>319.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>27.4</v>
@@ -2009,22 +2000,22 @@
         <v>14.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>22.8</v>
+        <v>2.2</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>1.8</v>
+        <v>19.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
@@ -2036,16 +2027,16 @@
         <v>23.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>8.6</v>
+        <v>20.2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>13.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>23.4</v>
@@ -2057,7 +2048,7 @@
         <v>21.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>7.6</v>
@@ -2078,7 +2069,7 @@
       <c r="C20" s="3" t="n">
         <v>358.8</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E20" s="3" t="n">
@@ -2097,7 +2088,7 @@
         <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>53.1</v>
+        <v>3.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2109,13 +2100,13 @@
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>22.8</v>
@@ -2123,11 +2114,11 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>1891.8</v>
+        <v>28.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
@@ -2161,7 +2152,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2284.2</v>
+        <v>284.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>68.09999999999999</v>
@@ -2172,14 +2163,14 @@
       <c r="F21" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>71.8</v>
+      <c r="G21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
@@ -2194,26 +2185,26 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>22</v>
@@ -2247,13 +2238,13 @@
         <v>339.2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>92.3</v>
+        <v>22.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.6</v>
@@ -2265,7 +2256,7 @@
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2277,7 +2268,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2.8</v>
+        <v>28</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2295,7 +2286,7 @@
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>724</v>
+        <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2329,7 +2320,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1542.6</v>
+        <v>1548.6</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>137.6</v>
@@ -2338,19 +2329,19 @@
         <v>85</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>18.1</v>
+        <v>111.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>352.6</v>
+        <v>52.6</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>119.3</v>
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.6</v>
@@ -2359,10 +2350,10 @@
         <v>0.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.9</v>
+        <v>9.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2371,10 +2362,10 @@
       <c r="Q23" s="3" t="inlineStr"/>
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>215.8</v>
+        <v>115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>293.1</v>
+        <v>393.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>33.2</v>
@@ -2386,13 +2377,13 @@
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>110.9</v>
+        <v>1103.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>606.8</v>
+        <v>16.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2413,26 +2404,26 @@
       <c r="D24" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="E24" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>29.2</v>
+        <v>22.2</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>184.8</v>
+      <c r="H24" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>48.1</v>
@@ -2441,7 +2432,7 @@
         <v>17.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>93.8</v>
@@ -2449,14 +2440,14 @@
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>10.1</v>
+      <c r="Q24" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>78.7</v>
@@ -2465,19 +2456,19 @@
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>8181.1</v>
+      <c r="X24" s="3" t="n">
+        <v>228.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2505,24 +2496,24 @@
         <v>21.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>9.4</v>
@@ -2543,16 +2534,16 @@
         <v>82.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>54.4</v>
+        <v>4.7</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>262.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2574,7 +2565,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.1</v>
+        <v>341.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.8</v>
@@ -2586,22 +2577,22 @@
         <v>20.3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>17</v>
+        <v>28.2</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>16.7</v>
@@ -2621,7 +2612,7 @@
       <c r="R26" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="S26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T26" s="3" t="n">
@@ -2630,7 +2621,7 @@
       <c r="U26" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2698,13 +2689,13 @@
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>22.7</v>
@@ -2721,14 +2712,14 @@
       <c r="W27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2735,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>45.3</v>
+        <v>453.6</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>28.8</v>
@@ -2756,7 +2747,7 @@
       <c r="G28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2771,14 +2762,14 @@
       <c r="L28" s="3" t="n">
         <v>46.1</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>840.6</v>
+        <v>24</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.1</v>
@@ -2787,10 +2778,10 @@
         <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>18.4</v>
+        <v>28.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>74.7</v>
@@ -2801,11 +2792,11 @@
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="8" t="n">
-        <v>864.1</v>
+      <c r="W28" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>77.5</v>
@@ -2833,7 +2824,7 @@
         <v>26.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>21.4</v>
@@ -2860,7 +2851,7 @@
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.4</v>
+        <v>18.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
@@ -2872,9 +2863,9 @@
         <v>22</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S29" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2884,7 +2875,7 @@
         <v>4.8</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>18.8</v>
@@ -2912,13 +2903,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>178.8</v>
+        <v>1788.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>138.4</v>
+        <v>131.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>814.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>106.4</v>
@@ -2927,10 +2918,10 @@
         <v>50</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>710.7</v>
+        <v>70.7</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.3</v>
@@ -2939,46 +2930,46 @@
         <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1434.5</v>
+        <v>454.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>58.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>114.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>200.2</v>
+        <v>100.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>392.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>230.3</v>
+        <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>111.8</v>
+        <v>161.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>998.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.1</v>
+        <v>116.1</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -2999,8 +2990,8 @@
       <c r="C31" s="3" t="n">
         <v>357.7</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <v>63.1</v>
+      <c r="D31" s="3" t="n">
+        <v>26.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>16.3</v>
@@ -3009,62 +3000,62 @@
         <v>21.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>96.09999999999999</v>
+      <c r="I31" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>28.9</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>372.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>66.2</v>
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1.1</v>
+        <v>25.1</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3085,20 +3076,20 @@
       <c r="D32" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1311.8</v>
+        <v>130.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr"/>
@@ -3109,23 +3100,23 @@
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.9</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1844151.8</v>
+        <v>2611.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.7</v>
@@ -3133,7 +3124,7 @@
       <c r="V32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3143,7 +3134,7 @@
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3167,8 +3158,8 @@
       <c r="E33" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>25.1</v>
+      <c r="F33" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.1</v>
@@ -3180,7 +3171,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>18.9</v>
+        <v>3.9</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
@@ -3192,7 +3183,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>78</v>
@@ -3213,22 +3204,22 @@
         <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>28</v>
+      <c r="W33" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>12.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>286.5</v>
+        <v>86</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3256,43 +3247,43 @@
         <v>20.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
@@ -3301,7 +3292,7 @@
         <v>7.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>18.8</v>
@@ -3355,14 +3346,14 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>80</v>
@@ -3374,13 +3365,13 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S35" s="8" t="n">
-        <v>28.1</v>
+        <v>19.7</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>6.7</v>
@@ -3398,7 +3389,7 @@
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3414,7 +3405,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>35.6</v>
+        <v>356.8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>28.1</v>
@@ -3428,7 +3419,7 @@
       <c r="G36" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3447,10 +3438,10 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>13.6</v>
+        <v>19.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.5</v>
@@ -3465,16 +3456,16 @@
         <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>168.2</v>
+        <v>60.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>20.8</v>
+      <c r="V36" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3483,7 +3474,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>41.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3499,10 +3490,10 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>164.3</v>
+        <v>1643.2</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>231.4</v>
+        <v>131.4</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>82.90000000000001</v>
@@ -3514,7 +3505,7 @@
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>710.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>10.5</v>
@@ -3524,31 +3515,31 @@
         <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>17.8</v>
+        <v>77</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>899.8</v>
+        <v>839.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>222.9</v>
+        <v>112.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>103.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>9383.4</v>
+        <v>385.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>34.2</v>
@@ -3558,13 +3549,13 @@
         <v>923.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>218.7</v>
+        <v>148.7</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3580,16 +3571,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>329.6</v>
+        <v>328.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E38" s="8" t="n">
-        <v>66.09999999999999</v>
+      <c r="E38" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.699999999999999</v>
@@ -3602,52 +3593,52 @@
         <v>3.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>688.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>16.1</v>
+        <v>11.6</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
-        <v>225.1</v>
+      <c r="Q38" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="S38" s="3" t="n">
+        <v>208.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8971.799999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3690,24 +3681,24 @@
       <c r="L39" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.8</v>
+      <c r="M39" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R39" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
@@ -3718,7 +3709,7 @@
         <v>16.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3747,7 +3738,7 @@
         <v>15.8</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>9.800000000000001</v>
@@ -3764,14 +3755,14 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
-        <v>7.9</v>
+      <c r="L40" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>82.5</v>
@@ -3785,14 +3776,14 @@
       <c r="R40" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="S40" s="8" t="n">
+      <c r="S40" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20</v>
@@ -3807,7 +3798,7 @@
         <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3832,17 +3823,17 @@
         <v>15.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H41" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.2</v>
@@ -3850,11 +3841,11 @@
       <c r="L41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>55.3</v>
+      <c r="M41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>76.2</v>
@@ -3868,14 +3859,14 @@
       <c r="R41" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>9.4</v>
+      <c r="S41" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="U41" s="8" t="n">
-        <v>18.8</v>
+      <c r="U41" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>4.4</v>
@@ -3890,7 +3881,7 @@
         <v>86.2</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3915,10 +3906,10 @@
         <v>17</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>22.9</v>
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>14.1</v>
@@ -3937,13 +3928,13 @@
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.8</v>
+        <v>2.6</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>682</v>
+        <v>62</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>26</v>
@@ -3952,7 +3943,7 @@
         <v>19.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>57.9</v>
@@ -3970,7 +3961,7 @@
         <v>20.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28.5</v>
+        <v>70.5</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -3989,7 +3980,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>742.6</v>
+        <v>442.6</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>27.6</v>
@@ -4000,47 +3991,47 @@
       <c r="F43" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>88.5</v>
+      <c r="G43" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>88</v>
+      <c r="L43" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>1.9</v>
+        <v>19.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>55.5</v>
       </c>
-      <c r="U43" s="8" t="n">
+      <c r="U43" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="V43" s="3" t="n">
@@ -4049,11 +4040,11 @@
       <c r="W43" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>18.5</v>
+      <c r="X43" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>20.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>7.1</v>
@@ -4111,7 +4102,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1889</v>
+        <v>1839</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>134.4</v>
@@ -4121,43 +4112,43 @@
         <v>108.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>59.5</v>
+        <v>52.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>69.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>117.4</v>
+        <v>17.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>53.7</v>
+        <v>23.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>71</v>
+        <v>11.6</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1405.5</v>
+        <v>405.5</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1268.4</v>
+        <v>125.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>101.8</v>
+        <v>101</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>104.8</v>
+        <v>104.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>330</v>
@@ -4169,16 +4160,16 @@
         <v>104.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>98.5</v>
+        <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>118.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>108.8</v>
+        <v>108.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11.4</v>
+        <v>21.4</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4194,7 +4185,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>362.9</v>
+        <v>367.9</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>26.9</v>
@@ -4203,28 +4194,28 @@
         <v>16.4</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>65.90000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>1.6</v>
@@ -4233,37 +4224,37 @@
         <v>81.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="W46" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
